--- a/data/workbooks/test2-marking.xlsx
+++ b/data/workbooks/test2-marking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude\DoktoraTez\AI-Tests\github\data\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102C1F3F-97CC-43FF-8B57-E546FE711887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A2988B-10D9-403D-9AB9-EF2077130304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="521">
   <si>
     <t>ady-kbd AI Language Testing Tool</t>
   </si>
@@ -1807,22 +1807,19 @@
     <t>doğru / правильно</t>
   </si>
   <si>
-    <t>Türkçe açıklama metni kiril yazı sistemi kullanarak yazılmış.</t>
-  </si>
-  <si>
-    <t>шӏу kelimesi eksik kalmış.</t>
-  </si>
-  <si>
-    <t>Parantez içindeki Türkçe açıklama kiril harfleri ile yazılmış.</t>
-  </si>
-  <si>
-    <t>Parantez içindeki Türkçe açıklama kiril harfi д ile başlayarak yazılmış.</t>
-  </si>
-  <si>
-    <t>Türkçe açıklamanın son harfi büyük harf yazılmış.</t>
-  </si>
-  <si>
     <t>имэфэ дахэ ifadesini Rusça tanımladığı şekle bağlı olarak kabul ettik.</t>
+  </si>
+  <si>
+    <t>Gerçek farkı buldu, ama olmayan farklar da üretti.</t>
+  </si>
+  <si>
+    <t>Fark yok dedi.</t>
+  </si>
+  <si>
+    <t>Gerçek farkı buldu.</t>
+  </si>
+  <si>
+    <t>Yazı sistemi karışıklığı.</t>
   </si>
 </sst>
 </file>
@@ -4197,7 +4194,9 @@
       <c r="L32" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="M32" s="5"/>
+      <c r="M32" s="5" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="33" spans="1:13" ht="114" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
@@ -4236,7 +4235,9 @@
       <c r="L33" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="M33" s="5"/>
+      <c r="M33" s="5" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="34" spans="1:13" ht="185.25" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
@@ -4275,7 +4276,9 @@
       <c r="L34" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="M34" s="5"/>
+      <c r="M34" s="5" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="35" spans="1:13" ht="256.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
@@ -4314,7 +4317,9 @@
       <c r="L35" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="M35" s="5"/>
+      <c r="M35" s="5" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="36" spans="1:13" ht="114" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
@@ -4353,7 +4358,9 @@
       <c r="L36" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="M36" s="5"/>
+      <c r="M36" s="5" t="s">
+        <v>517</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
@@ -8809,7 +8816,7 @@
       </c>
       <c r="T101" s="5"/>
     </row>
-    <row r="102" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>255</v>
       </c>
@@ -8829,17 +8836,15 @@
         <v>3</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H102" s="4"/>
-      <c r="I102" s="4">
-        <v>1</v>
-      </c>
+      <c r="I102" s="4"/>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
       <c r="L102" s="3">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M102" s="4"/>
       <c r="N102" s="4"/>
@@ -10094,7 +10099,7 @@
         <v>0</v>
       </c>
       <c r="T131" s="5" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="132" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
@@ -10311,7 +10316,7 @@
       </c>
       <c r="T136" s="5"/>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>263</v>
       </c>
@@ -10331,15 +10336,17 @@
         <v>3</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
+      <c r="I137" s="4">
+        <v>1</v>
+      </c>
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
       <c r="L137" s="3">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
@@ -11503,9 +11510,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T164" s="5" t="s">
-        <v>517</v>
-      </c>
+      <c r="T164" s="5"/>
     </row>
     <row r="165" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
@@ -12093,7 +12098,7 @@
       </c>
       <c r="T177" s="5"/>
     </row>
-    <row r="178" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>286</v>
       </c>
@@ -12136,7 +12141,7 @@
         <v>0</v>
       </c>
       <c r="T178" s="5" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="179" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
@@ -12229,7 +12234,7 @@
       </c>
       <c r="T180" s="5"/>
     </row>
-    <row r="181" spans="1:20" ht="57" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>288</v>
       </c>
@@ -12272,7 +12277,7 @@
         <v>0</v>
       </c>
       <c r="T181" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="182" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
@@ -12761,7 +12766,7 @@
       </c>
       <c r="T192" s="5"/>
     </row>
-    <row r="193" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>290</v>
       </c>
@@ -12805,9 +12810,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T193" s="5" t="s">
-        <v>520</v>
-      </c>
+      <c r="T193" s="5"/>
     </row>
     <row r="194" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
@@ -13120,7 +13123,7 @@
         <v>0</v>
       </c>
       <c r="T200" s="5" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="201" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
@@ -13367,7 +13370,7 @@
       </c>
       <c r="D7" s="3">
         <f>SUMIFS(Sentences!$I:$I,Sentences!$C:$C,"3")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3">
         <f>SUMIFS(Sentences!$J:$J,Sentences!$C:$C,"3")</f>
@@ -13379,11 +13382,11 @@
       </c>
       <c r="G7" s="3">
         <f>C7+D7+E7+F7</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7" s="3">
         <f>IF(B7=0,0,(C7+D7+E7+F7)*100/B7)</f>
-        <v>16.722408026755854</v>
+        <v>17.056856187290968</v>
       </c>
       <c r="I7" s="3">
         <f>SUMIFS(Sentences!$M:$M,Sentences!$C:$C,"3")</f>
@@ -13441,7 +13444,7 @@
       </c>
       <c r="D9" s="3">
         <f>SUMIFS(Sentences!$I:$I,Sentences!$C:$C,"5")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3">
         <f>SUMIFS(Sentences!$J:$J,Sentences!$C:$C,"5")</f>
@@ -13453,11 +13456,11 @@
       </c>
       <c r="G9" s="3">
         <f>C9+D9+E9+F9</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H9" s="3">
         <f>IF(B9=0,0,(C9+D9+E9+F9)*100/B9)</f>
-        <v>17.721518987341771</v>
+        <v>17.088607594936708</v>
       </c>
       <c r="I9" s="3">
         <f>SUMIFS(Sentences!$M:$M,Sentences!$C:$C,"5")</f>
@@ -13523,11 +13526,11 @@
       </c>
       <c r="B15" s="3">
         <f>COUNTIFS(Sentences!$C:$C,"3",Sentences!$G:$G,"doğru / правильно")</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3">
         <f>COUNTIFS(Sentences!$C:$C,"3",Sentences!$G:$G,"yanlış ama anlaşılır / понятно")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" s="3">
         <f>COUNTIFS(Sentences!$C:$C,"3",Sentences!$G:$G,"yanlış ve anlamsız / непонятно")</f>
@@ -13557,11 +13560,11 @@
       </c>
       <c r="B17" s="3">
         <f>COUNTIFS(Sentences!$C:$C,"5",Sentences!$G:$G,"doğru / правильно")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3">
         <f>COUNTIFS(Sentences!$C:$C,"5",Sentences!$G:$G,"yanlış ama anlaşılır / понятно")</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="3">
         <f>COUNTIFS(Sentences!$C:$C,"5",Sentences!$G:$G,"yanlış ve anlamsız / непонятно")</f>
